--- a/conformance/fixtures/019-filename-empty-basename-error/template.xlsx
+++ b/conformance/fixtures/019-filename-empty-basename-error/template.xlsx
@@ -26,7 +26,7 @@
     <t>Data</t>
   </si>
   <si>
-    <t>header_row</t>
+    <t>source_table</t>
   </si>
   <si>
     <t>1</t>
@@ -455,7 +455,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -476,6 +476,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/conformance/fixtures/019-filename-empty-basename-error/template.xlsx
+++ b/conformance/fixtures/019-filename-empty-basename-error/template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="_config" state="hidden" r:id="rId4"/>
+    <sheet sheetId="1" name="__config__" state="hidden" r:id="rId4"/>
     <sheet sheetId="2" name="Report" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -455,7 +455,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -476,6 +476,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/conformance/fixtures/019-filename-empty-basename-error/template.xlsx
+++ b/conformance/fixtures/019-filename-empty-basename-error/template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>name</t>
   </si>
@@ -35,7 +35,13 @@
     <t>output_file_pattern</t>
   </si>
   <si>
-    <t>{{ [Name] }}.xlsx</t>
+    <t>{{ __config__[suffix] }}.xlsx</t>
+  </si>
+  <si>
+    <t>suffix</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Item</t>
@@ -418,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -451,6 +457,14 @@
       </c>
       <c r="B4" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -466,12 +480,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
